--- a/python_data_analysis/cluster_separation_data.xlsx
+++ b/python_data_analysis/cluster_separation_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\C++\slime_mold_simulation\slime_mold_simulation\python_data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B58F09-BA62-4BDA-A167-8E17B8C8C3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4468AC5-498B-4F11-85CE-2A640258E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -393,18 +393,18 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.31017603066104799</v>
+        <v>0.31101740991772597</v>
       </c>
       <c r="C2">
-        <v>0.119649733541942</v>
+        <v>6.2430009078410099E-2</v>
       </c>
       <c r="D2">
         <f>(1/B2)</f>
-        <v>3.2239757465101264</v>
+        <v>3.2152540922533306</v>
       </c>
       <c r="E2">
         <f>D2*(C2/B2)</f>
-        <v>1.243641677255052</v>
+        <v>0.64539262358936655</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">

--- a/python_data_analysis/cluster_separation_data.xlsx
+++ b/python_data_analysis/cluster_separation_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\C++\slime_mold_simulation\slime_mold_simulation\python_data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4468AC5-498B-4F11-85CE-2A640258E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7DA840-3570-425C-A155-7B688604041E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -393,18 +393,18 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.31101740991772597</v>
+        <v>0.30668000000000001</v>
       </c>
       <c r="C2">
-        <v>6.2430009078410099E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="D2">
         <f>(1/B2)</f>
-        <v>3.2152540922533306</v>
+        <v>3.2607277944437199</v>
       </c>
       <c r="E2">
         <f>D2*(C2/B2)</f>
-        <v>0.64539262358936655</v>
+        <v>3.8276444698048098E-2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -412,18 +412,18 @@
         <v>21.33</v>
       </c>
       <c r="B3">
-        <v>0.301877638247322</v>
+        <v>0.29426999999999998</v>
       </c>
       <c r="C3">
-        <v>7.2994480903860195E-2</v>
+        <v>3.0400000000000002E-3</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D11" si="0">(1/B3)</f>
-        <v>3.3126004489962289</v>
+        <v>3.3982397118292726</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E11" si="1">D3*(C3/B3)</f>
-        <v>0.80099192381474449</v>
+        <v>3.5106020742722635E-2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -431,18 +431,18 @@
         <v>26.67</v>
       </c>
       <c r="B4">
-        <v>0.28598118250821702</v>
+        <v>0.29416999999999999</v>
       </c>
       <c r="C4">
-        <v>4.62037868052083E-2</v>
+        <v>3.0699999999999998E-3</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>3.4967335655774039</v>
+        <v>3.3993949077064283</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>0.56494042986171689</v>
+        <v>3.5476569217319016E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -450,18 +450,18 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>0.28210310876248601</v>
+        <v>0.29271999999999998</v>
       </c>
       <c r="C5">
-        <v>6.5976966114875302E-2</v>
+        <v>3.63E-3</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>3.5448031905310917</v>
+        <v>3.416233943700465</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>0.82904212226346219</v>
+        <v>4.236447531987117E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -469,18 +469,18 @@
         <v>37.340000000000003</v>
       </c>
       <c r="B6">
-        <v>0.27109268630576899</v>
+        <v>0.27649000000000001</v>
       </c>
       <c r="C6">
-        <v>5.8745002622009802E-2</v>
+        <v>5.9800000000000001E-3</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>3.688775280614125</v>
+        <v>3.616767333357445</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
-        <v>0.79934695577610015</v>
+        <v>7.8224415542976308E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -488,18 +488,37 @@
         <v>42.67</v>
       </c>
       <c r="B7">
-        <v>0.28420762159271001</v>
+        <v>0.28226000000000001</v>
       </c>
       <c r="C7">
-        <v>0.10224130800009899</v>
+        <v>2.7200000000000002E-3</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>3.5185544792780821</v>
+        <v>3.5428328491461771</v>
       </c>
       <c r="E7">
         <f t="shared" si="1"/>
-        <v>1.265770461098098</v>
+        <v>3.414052770381068E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>48</v>
+      </c>
+      <c r="B8">
+        <v>0.27705000000000002</v>
+      </c>
+      <c r="C8">
+        <v>4.1799999999999997E-3</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>3.6094567767550982</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>5.4457784973240601E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -507,18 +526,18 @@
         <v>53.33</v>
       </c>
       <c r="B9">
-        <v>0.26752119723461998</v>
+        <v>0.27296999999999999</v>
       </c>
       <c r="C9">
-        <v>9.3745620070422003E-2</v>
+        <v>3.3800000000000002E-3</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>3.7380215487110933</v>
+        <v>3.6634062351174124</v>
       </c>
       <c r="E9">
         <f t="shared" si="1"/>
-        <v>1.309889278094081</v>
+        <v>4.5361442923020308E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -526,18 +545,18 @@
         <v>58.67</v>
       </c>
       <c r="B10">
-        <v>0.25779386681891903</v>
+        <v>0.26551000000000002</v>
       </c>
       <c r="C10">
-        <v>4.70049124609681E-2</v>
+        <v>2.7799999999999999E-3</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>3.8790682351742118</v>
+        <v>3.766336484501525</v>
       </c>
       <c r="E10">
         <f t="shared" si="1"/>
-        <v>0.70729092617460432</v>
+        <v>3.9435107630274704E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -545,18 +564,18 @@
         <v>64</v>
       </c>
       <c r="B11">
-        <v>0.24855185846740399</v>
+        <v>0.25886999999999999</v>
       </c>
       <c r="C11">
-        <v>1.3168185645348E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>4.0233052617916503</v>
+        <v>3.862942789817283</v>
       </c>
       <c r="E11">
         <f t="shared" si="1"/>
-        <v>0.2131532265413571</v>
+        <v>3.7305817493503333E-2</v>
       </c>
     </row>
   </sheetData>
